--- a/data/trans_orig/IP3110_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48144</t>
+          <t>48083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49156</t>
+          <t>49803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69397</t>
+          <t>69045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77341</t>
+          <t>77871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110387</t>
+          <t>111856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140833</t>
+          <t>141735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85656</t>
+          <t>86055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>46967</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>22082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>53012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61032</t>
+          <t>62036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90045</t>
+          <t>90810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64903</t>
+          <t>64147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74734</t>
+          <t>76988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104717</t>
+          <t>104179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148051</t>
+          <t>148192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185216</t>
+          <t>185537</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>53448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>51912</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78953</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54488</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61413</t>
+          <t>62684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95318</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85860</t>
+          <t>82111</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>141093</t>
+          <t>140181</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>113851</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154636</t>
+          <t>156336</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>214333</t>
+          <t>217012</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>284891</t>
+          <t>284644</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129405</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64083</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111097</t>
+          <t>111017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126172</t>
+          <t>125506</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226533</t>
+          <t>213792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53413</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42805</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77177</t>
+          <t>75587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70858</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>101199</t>
+          <t>103231</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>100453</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>139570</t>
+          <t>139248</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>147416</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>218872</t>
+          <t>219720</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>270935</t>
+          <t>273279</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>227127</t>
+          <t>231260</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292417</t>
+          <t>293671</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>280156</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>333335</t>
+          <t>336364</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>532236</t>
+          <t>531070</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>613258</t>
+          <t>619216</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>113773</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>226612</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>192477</t>
+          <t>191386</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>265888</t>
+          <t>263680</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>368978</t>
+          <t>373524</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>68306</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>105084</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>129866</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>174260</t>
+          <t>175909</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3110_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16148</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11429</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21505</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10580</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6866</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14502</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9729</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5844</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14819</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11594</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16250</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30,97%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12292</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8633</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17056</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,44%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7475</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8931</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6430</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2306</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5553</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>164</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12475</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18363</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11704</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7046</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18014</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36232</t>
+          <t>33370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32532</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24764</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40838</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,1%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>32808</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24644</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>42696</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>26,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37783</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>36537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>60928</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84295</t>
+          <t>72155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57941</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49583</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68310</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>59086</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49803</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>69045</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66916</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>47371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77871</t>
+          <t>65505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126002</t>
+          <t>113613</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111856</t>
+          <t>100427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141735</t>
+          <t>126582</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46051</t>
+          <t>39575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72300</t>
+          <t>63392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>52489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>74638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13617</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27354</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14641</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9593</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>21122</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>33109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46967</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7696</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>156480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>156480</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>156480</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>158778</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>158778</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>158778</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>145081</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>145081</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145081</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>180248</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>180248</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>180248</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>531</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>339025</t>
+          <t>301561</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339025</t>
+          <t>301561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339025</t>
+          <t>301561</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29986</t>
+          <t>26075</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>37582</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>27635</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>48386</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35721</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>27083</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>46021</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39783</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>47271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>75504</t>
+          <t>74751</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>62913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90810</t>
+          <t>89458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>86535</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>74230</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>100558</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>43,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>50,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>75658</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>64147</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>88674</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>43,71%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>37,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>90915</t>
+          <t>72269</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104179</t>
+          <t>83702</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>166573</t>
+          <t>158804</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148192</t>
+          <t>141238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185537</t>
+          <t>175656</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>34119</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>25450</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>44461</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>25949</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>19104</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>34564</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>64746</t>
+          <t>61786</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>49752</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80166</t>
+          <t>74792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>29453</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40031</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>24289</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16755</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32263</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>51984</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65222</t>
+          <t>68748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -2875,57 +2875,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8962</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8483</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>15929</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9400</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>13372</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>7876</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>21162</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>13267</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>7404</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>20193</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>34048</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>25128</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>41741</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>28445</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>54186</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48640</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62684</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96384</t>
+          <t>92016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>126840</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>110154</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>144754</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>120811</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>82111</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>140181</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>44,59%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>51,74%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>135423</t>
+          <t>119967</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>113851</t>
+          <t>105408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156336</t>
+          <t>135162</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>256234</t>
+          <t>246806</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>217012</t>
+          <t>223014</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>284644</t>
+          <t>270124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>77747</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>63709</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>100622</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>74714</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>49702</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>134722</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>81114</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>41258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111017</t>
+          <t>65713</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>155828</t>
+          <t>130875</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>112659</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>213792</t>
+          <t>158870</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>34428</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>24150</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>50242</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>22741</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>14947</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>31988</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>59589</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75587</t>
+          <t>78188</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10412</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5362</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>17900</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>11914</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>17036</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23615</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>251885</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>251885</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>251885</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>304999</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>679</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>575915</t>
+          <t>544106</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>575915</t>
+          <t>544106</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>575915</t>
+          <t>544106</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>37952</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>29225</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>50485</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>40373</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>30128</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>51529</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71348</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103231</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>114742</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>96436</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>133940</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>119999</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>100603</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>139248</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>147416</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>245846</t>
+          <t>231596</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>219720</t>
+          <t>208301</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>282909</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>257184</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>307842</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>385</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>267846</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>231260</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>293671</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>307608</t>
+          <t>259757</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>278181</t>
+          <t>239151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>336364</t>
+          <t>280857</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>575455</t>
+          <t>542665</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>531070</t>
+          <t>510163</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>619216</t>
+          <t>575200</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>146995</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>126823</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>174502</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>141807</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>112716</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>210872</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>160247</t>
+          <t>117630</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>136519</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>191386</t>
+          <t>135713</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>264625</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>263680</t>
+          <t>237938</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>373524</t>
+          <t>294409</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>84926</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>105762</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>50861</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>77311</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>152419</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>128320</t>
+          <t>130850</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>175909</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>14818</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>9258</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>21321</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>649260</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>614318</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1850</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1392282</t>
+          <t>1300580</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
